--- a/GeminiTest/GeminiTest.xlsx
+++ b/GeminiTest/GeminiTest.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jacqui\Power Electronic Circuit Papers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jacqui\PowerVision\GeminiTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94FAF4DD-966D-457B-84CD-7611631E1237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414969CF-58F3-4539-964F-57D4B2451544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6132" yWindow="1284" windowWidth="20676" windowHeight="15276" xr2:uid="{AC2F5387-ECEB-4A62-81FD-9A95B1A58C21}"/>
+    <workbookView xWindow="9624" yWindow="1176" windowWidth="20676" windowHeight="15276" xr2:uid="{AC2F5387-ECEB-4A62-81FD-9A95B1A58C21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>#correct_comp/#all_comp</t>
   </si>
@@ -172,6 +172,78 @@
   </si>
   <si>
     <t>也是根据ICC的拓扑硬编造出了一些component</t>
+  </si>
+  <si>
+    <r>
+      <t>有</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>输入 L-C 滤波器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Buck 变换器 (Buck Converter)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，并且在电感支路中考虑了寄生电阻</t>
+    </r>
+  </si>
+  <si>
+    <t>生硬地按照识别的拓扑结构编造了两个多余的resistor</t>
+  </si>
+  <si>
+    <t>SEPIC</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">标准的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>升压变换器 (Boost Converter)</t>
+    </r>
+  </si>
+  <si>
+    <t>diode，inductor connection wrong</t>
   </si>
 </sst>
 </file>
@@ -338,12 +410,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -693,35 +764,34 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.88671875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="31.21875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="18" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13" style="9" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="4"/>
+    <col min="2" max="2" width="23.88671875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="31.21875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="18" style="8" customWidth="1"/>
+    <col min="6" max="6" width="13" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -729,88 +799,88 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="13">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="12">
         <v>1</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <f>SUM(D:D)</f>
-        <v>7</v>
-      </c>
-      <c r="H2" s="15">
+        <v>11</v>
+      </c>
+      <c r="H2" s="14">
         <f>COUNTA(D:D)-1</f>
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="13">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="12">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="7"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="13">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="13">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="12">
         <v>1</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="13">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>0</v>
       </c>
       <c r="E7" t="s">
@@ -818,12 +888,12 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="13">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="12">
         <v>1</v>
       </c>
       <c r="E8" t="s">
@@ -831,44 +901,95 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="12">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
+      <c r="C10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="12">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="12">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <v>0</v>
       </c>
       <c r="E15" t="s">
@@ -876,38 +997,38 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <v>0</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <v>0</v>
       </c>
       <c r="E18" t="s">
@@ -915,947 +1036,947 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="5">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="5">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="5">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="5">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5">
+      <c r="A54" s="4">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5">
+      <c r="A56" s="4">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5">
+      <c r="A60" s="4">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5">
+      <c r="A64" s="4">
         <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5">
+      <c r="A70" s="4">
         <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5">
+      <c r="A72" s="4">
         <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5">
+      <c r="A74" s="4">
         <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5">
+      <c r="A75" s="4">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5">
+      <c r="A76" s="4">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="5">
+      <c r="A77" s="4">
         <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="5">
+      <c r="A78" s="4">
         <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="5">
+      <c r="A80" s="4">
         <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5">
+      <c r="A82" s="4">
         <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5">
+      <c r="A83" s="4">
         <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5">
+      <c r="A84" s="4">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="5">
+      <c r="A85" s="4">
         <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="5">
+      <c r="A86" s="4">
         <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5">
+      <c r="A87" s="4">
         <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5">
+      <c r="A88" s="4">
         <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5">
+      <c r="A89" s="4">
         <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5">
+      <c r="A90" s="4">
         <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5">
+      <c r="A91" s="4">
         <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5">
+      <c r="A92" s="4">
         <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5">
+      <c r="A93" s="4">
         <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="5">
+      <c r="A94" s="4">
         <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5">
+      <c r="A95" s="4">
         <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5">
+      <c r="A96" s="4">
         <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="5">
+      <c r="A97" s="4">
         <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="5">
+      <c r="A98" s="4">
         <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="5">
+      <c r="A99" s="4">
         <v>98</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="13">
+      <c r="D99" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="5">
+      <c r="A100" s="4">
         <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="5">
+      <c r="A101" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="5">
+      <c r="A102" s="4">
         <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="5">
+      <c r="A103" s="4">
         <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="5">
+      <c r="A104" s="4">
         <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="5">
+      <c r="A105" s="4">
         <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="5">
+      <c r="A106" s="4">
         <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="5">
+      <c r="A107" s="4">
         <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="5">
+      <c r="A108" s="4">
         <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
         <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="5">
+      <c r="A110" s="4">
         <v>109</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C110" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D110" s="13">
+      <c r="D110" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="5">
+      <c r="A111" s="4">
         <v>110</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="5">
+      <c r="A112" s="4">
         <v>111</v>
       </c>
-      <c r="C112" s="9" t="s">
+      <c r="C112" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D112" s="13">
+      <c r="D112" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="5">
+      <c r="A113" s="4">
         <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="5">
+      <c r="A114" s="4">
         <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="5">
+      <c r="A115" s="4">
         <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="5">
+      <c r="A116" s="4">
         <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="5">
+      <c r="A117" s="4">
         <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="5">
+      <c r="A118" s="4">
         <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="5">
+      <c r="A119" s="4">
         <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="5">
+      <c r="A120" s="4">
         <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="5">
+      <c r="A121" s="4">
         <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="5">
+      <c r="A122" s="4">
         <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="5">
+      <c r="A123" s="4">
         <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="5">
+      <c r="A124" s="4">
         <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="5">
+      <c r="A125" s="4">
         <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="5">
+      <c r="A126" s="4">
         <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="5">
+      <c r="A127" s="4">
         <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="5">
+      <c r="A128" s="4">
         <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="5">
+      <c r="A129" s="4">
         <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="5">
+      <c r="A130" s="4">
         <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="5">
+      <c r="A131" s="4">
         <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="5">
+      <c r="A132" s="4">
         <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="5">
+      <c r="A133" s="4">
         <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="5">
+      <c r="A134" s="4">
         <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="5">
+      <c r="A135" s="4">
         <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="5">
+      <c r="A136" s="4">
         <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="5">
+      <c r="A137" s="4">
         <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="5">
+      <c r="A138" s="4">
         <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="5">
+      <c r="A139" s="4">
         <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="5">
+      <c r="A140" s="4">
         <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="5">
+      <c r="A141" s="4">
         <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="5">
+      <c r="A142" s="4">
         <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" s="5">
+      <c r="A143" s="4">
         <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" s="5">
+      <c r="A144" s="4">
         <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" s="5">
+      <c r="A145" s="4">
         <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" s="5">
+      <c r="A146" s="4">
         <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" s="5">
+      <c r="A147" s="4">
         <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" s="5">
+      <c r="A148" s="4">
         <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="5">
+      <c r="A149" s="4">
         <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="5">
+      <c r="A150" s="4">
         <v>149</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="5">
+      <c r="A151" s="4">
         <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" s="5">
+      <c r="A152" s="4">
         <v>151</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" s="5">
+      <c r="A153" s="4">
         <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" s="5">
+      <c r="A154" s="4">
         <v>153</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" s="5">
+      <c r="A155" s="4">
         <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" s="5">
+      <c r="A156" s="4">
         <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" s="5">
+      <c r="A157" s="4">
         <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" s="5">
+      <c r="A158" s="4">
         <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" s="5">
+      <c r="A159" s="4">
         <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" s="5">
+      <c r="A160" s="4">
         <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" s="5">
+      <c r="A161" s="4">
         <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" s="5">
+      <c r="A162" s="4">
         <v>161</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" s="5">
+      <c r="A163" s="4">
         <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" s="5">
+      <c r="A164" s="4">
         <v>163</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" s="5">
+      <c r="A165" s="4">
         <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" s="5">
+      <c r="A166" s="4">
         <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" s="5">
+      <c r="A167" s="4">
         <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" s="5">
+      <c r="A168" s="4">
         <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" s="5">
+      <c r="A169" s="4">
         <v>168</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" s="5">
+      <c r="A170" s="4">
         <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="5">
+      <c r="A171" s="4">
         <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" s="5">
+      <c r="A172" s="4">
         <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" s="5">
+      <c r="A173" s="4">
         <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" s="5">
+      <c r="A174" s="4">
         <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A175" s="5">
+      <c r="A175" s="4">
         <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A176" s="5">
+      <c r="A176" s="4">
         <v>175</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A177" s="5">
+      <c r="A177" s="4">
         <v>176</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A178" s="5">
+      <c r="A178" s="4">
         <v>177</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A179" s="5">
+      <c r="A179" s="4">
         <v>178</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A180" s="5">
+      <c r="A180" s="4">
         <v>179</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A181" s="5">
+      <c r="A181" s="4">
         <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A182" s="5">
+      <c r="A182" s="4">
         <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A183" s="5">
+      <c r="A183" s="4">
         <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A184" s="5">
+      <c r="A184" s="4">
         <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A185" s="5">
+      <c r="A185" s="4">
         <v>184</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A186" s="5">
+      <c r="A186" s="4">
         <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A187" s="5">
+      <c r="A187" s="4">
         <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A188" s="5">
+      <c r="A188" s="4">
         <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A189" s="5">
+      <c r="A189" s="4">
         <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A190" s="5">
+      <c r="A190" s="4">
         <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A191" s="5">
+      <c r="A191" s="4">
         <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A192" s="5">
+      <c r="A192" s="4">
         <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" s="5">
+      <c r="A193" s="4">
         <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A194" s="5">
+      <c r="A194" s="4">
         <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A195" s="5">
+      <c r="A195" s="4">
         <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A196" s="5">
+      <c r="A196" s="4">
         <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A197" s="5">
+      <c r="A197" s="4">
         <v>196</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A198" s="5">
+      <c r="A198" s="4">
         <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A199" s="5">
+      <c r="A199" s="4">
         <v>198</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A200" s="5">
+      <c r="A200" s="4">
         <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A201" s="5">
+      <c r="A201" s="4">
         <v>200</v>
       </c>
     </row>
